--- a/cmd/build-excel/template/Template-KnToolsExcelAjs.xlsx
+++ b/cmd/build-excel/template/Template-KnToolsExcelAjs.xlsx
@@ -8,25 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\02.Kazu-Development\51.Go\knTools-go-jp1ajs\cmd\build-excel\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64150C75-14B1-4978-A5F8-1700386EAA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6974EEFE-FBEE-4CCE-AAC7-2C2A823F3DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1640" yWindow="4250" windowWidth="35590" windowHeight="14650" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="2280" windowWidth="26460" windowHeight="11990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="1" r:id="rId1"/>
-    <sheet name="Unit" sheetId="2" r:id="rId2"/>
-    <sheet name="Net" sheetId="6" r:id="rId3"/>
-    <sheet name="Job" sheetId="7" r:id="rId4"/>
-    <sheet name="File" sheetId="3" r:id="rId5"/>
-    <sheet name="Next" sheetId="4" r:id="rId6"/>
-    <sheet name="Ajsprint" sheetId="5" r:id="rId7"/>
+    <sheet name="Net" sheetId="6" r:id="rId2"/>
+    <sheet name="Job" sheetId="7" r:id="rId3"/>
+    <sheet name="File" sheetId="3" r:id="rId4"/>
+    <sheet name="Next" sheetId="4" r:id="rId5"/>
+    <sheet name="Ajsprint" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">File!$B$3:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Job!$B$3:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Net!$B$3:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Next!$B$3:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Unit!$B$3:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">File!$B$3:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Job!$B$3:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Net!$B$3:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Next!$B$3:$G$3</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
   <si>
     <t>Index</t>
     <phoneticPr fontId="1"/>
@@ -89,13 +87,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ファイル名</t>
-    <rPh sb="4" eb="5">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ユニット</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -282,50 +273,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>タイプ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>te コマンド</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>un</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>tho</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>eu</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>sd</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>st</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>cy</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>sh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>shd</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>de</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Net</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -335,6 +282,74 @@
   </si>
   <si>
     <t>Ajsprint</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>監視対象ファイル名</t>
+    <rPh sb="0" eb="2">
+      <t>カンシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>監視条件</t>
+    <rPh sb="0" eb="2">
+      <t>カンシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>監視間隔</t>
+    <rPh sb="0" eb="2">
+      <t>カンシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>監視条件成立</t>
+    <rPh sb="0" eb="2">
+      <t>カンシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジョブ実行時のJP1ユーザー</t>
+    <rPh sb="3" eb="5">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実行順序関係</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                   </t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -342,7 +357,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,6 +425,14 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -524,10 +547,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,12 +837,12 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.4140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="33.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
@@ -832,16 +855,16 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="B4" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="18">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
       <c r="C4" s="8"/>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>2</v>
       </c>
     </row>
@@ -853,7 +876,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -861,10 +884,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -872,10 +895,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -886,7 +909,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -897,7 +920,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -905,10 +928,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -928,85 +951,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{248A623B-DE8D-4A76-8003-4047BFEDBAE6}">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="12.1640625" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="16384" width="12.1640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" s="4" customFormat="1">
-      <c r="A1" s="3" t="str">
-        <f ca="1">MID(CELL("filename",A1),FIND("]",CELL("filename",A1))+1,31)</f>
-        <v>Unit</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="B3:P3" xr:uid="{248A623B-DE8D-4A76-8003-4047BFEDBAE6}"/>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="C1" location="Index!A1" display="Index!A1" xr:uid="{AB97B9E8-0341-4F2C-BE63-33196F6EA5F7}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B2B8391-FBA9-4CA3-89BA-2653E096B108}">
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="13.58203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="16384" width="13.58203125" style="1"/>
+    <col min="1" max="1" width="5.08203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="13.58203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="4" customFormat="1">
@@ -1015,7 +976,12 @@
         <v>Net</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="L2" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1023,34 +989,34 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1063,12 +1029,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC59FBA3-5435-4B9B-B990-2CB968D876C4}">
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="15.9140625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="16384" width="15.9140625" style="1"/>
+    <col min="1" max="1" width="5.08203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="48.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="15.9140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="4" customFormat="1">
@@ -1077,7 +1054,12 @@
         <v>Job</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="K2" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1085,31 +1067,31 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1122,47 +1104,69 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C65747-D33D-4A95-A29B-90783441B70B}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="5.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="4.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="5.1640625" style="1"/>
+    <col min="3" max="3" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="5.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1">
+    <row r="1" spans="1:10" s="4" customFormat="1">
       <c r="A1" s="3" t="str">
         <f ca="1">MID(CELL("filename",A1),FIND("]",CELL("filename",A1))+1,31)</f>
         <v>File</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="J2" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:F3" xr:uid="{D4C65747-D33D-4A95-A29B-90783441B70B}"/>
+  <autoFilter ref="B3:J3" xr:uid="{D4C65747-D33D-4A95-A29B-90783441B70B}"/>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="C1" location="Index!A1" display="Index!A1" xr:uid="{1A156D5C-7D60-4A22-825E-994F8574B492}"/>
@@ -1171,46 +1175,48 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60107372-B1F0-42D3-9EAC-5DE9C18ED781}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="5.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" style="1" customWidth="1"/>
-    <col min="3" max="6" width="17.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="1"/>
+    <col min="3" max="5" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1">
+    <row r="1" spans="1:7" s="4" customFormat="1">
       <c r="A1" s="3" t="str">
         <f ca="1">MID(CELL("filename",A1),FIND("]",CELL("filename",A1))+1,31)</f>
         <v>Next</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>22</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>8</v>
@@ -1219,11 +1225,14 @@
         <v>9</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:F3" xr:uid="{60107372-B1F0-42D3-9EAC-5DE9C18ED781}"/>
+  <autoFilter ref="B3:G3" xr:uid="{60107372-B1F0-42D3-9EAC-5DE9C18ED781}"/>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="C1" location="Index!A1" display="Index!A1" xr:uid="{E0FE6D13-1F31-42D6-919B-F8EE3E74DB7C}"/>
@@ -1232,13 +1241,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E344F394-E7C1-44E8-B039-E93C2BE9B3CA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" style="1"/>
-    <col min="3" max="3" width="96.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="103.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
@@ -1248,12 +1258,17 @@
         <v>Ajsprint</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="C2" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
